--- a/l9.xlsx
+++ b/l9.xlsx
@@ -29,11 +29,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,10 +62,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7715,7 +7712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K733"/>
+  <dimension ref="A1:K734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34712,6 +34709,33 @@
       </c>
       <c r="J733" t="inlineStr"/>
       <c r="K733" t="inlineStr"/>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr"/>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>كرد10</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr"/>
+      <c r="E734" t="inlineStr"/>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr"/>
+      <c r="H734" t="inlineStr"/>
+      <c r="I734" t="n">
+        <v>3</v>
+      </c>
+      <c r="J734" t="inlineStr"/>
+      <c r="K734" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -45217,7 +45241,7 @@
       <c r="E154" s="1" t="n">
         <v>46211</v>
       </c>
-      <c r="F154" s="2" t="n">
+      <c r="F154" s="1" t="n">
         <v>46218</v>
       </c>
       <c r="G154" t="inlineStr">

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -7712,7 +7712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K734"/>
+  <dimension ref="A1:K735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34736,6 +34736,33 @@
       </c>
       <c r="J734" t="inlineStr"/>
       <c r="K734" t="inlineStr"/>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr"/>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>كرد10</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr"/>
+      <c r="E735" t="inlineStr"/>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr"/>
+      <c r="H735" t="inlineStr"/>
+      <c r="I735" t="n">
+        <v>2</v>
+      </c>
+      <c r="J735" t="inlineStr"/>
+      <c r="K735" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -7712,7 +7712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K735"/>
+  <dimension ref="A1:K736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34763,6 +34763,45 @@
       </c>
       <c r="J735" t="inlineStr"/>
       <c r="K735" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr"/>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>سيرفيس</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>اعاده عيار ماكينه</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr"/>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>سيرفيس</t>
+        </is>
+      </c>
+      <c r="I736" t="n">
+        <v>5</v>
+      </c>
+      <c r="J736" t="inlineStr"/>
+      <c r="K736" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -7712,7 +7712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K736"/>
+  <dimension ref="A1:K737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34802,6 +34802,41 @@
       </c>
       <c r="J736" t="inlineStr"/>
       <c r="K736" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr"/>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>سيرفيس</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>تم تغير اول جريده خلفيه 240</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr"/>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="n">
+        <v>5</v>
+      </c>
+      <c r="J737" t="inlineStr"/>
+      <c r="K737" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -7712,7 +7712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K737"/>
+  <dimension ref="A1:K738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34837,6 +34837,41 @@
       </c>
       <c r="J737" t="inlineStr"/>
       <c r="K737" t="inlineStr"/>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr"/>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>تم تشغيل الماكينه اول مره</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>اعاده عيار ماكينه</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr"/>
+      <c r="G738" t="inlineStr"/>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="I738" t="n">
+        <v>3</v>
+      </c>
+      <c r="J738" t="inlineStr"/>
+      <c r="K738" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -29,9 +29,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -62,9 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7712,7 +7715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K738"/>
+  <dimension ref="A1:K739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34872,6 +34875,51 @@
       </c>
       <c r="J738" t="inlineStr"/>
       <c r="K738" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>0</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تغير اول جريده خلفي240</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تغير اول جريده خلفي240' بواسطة بل</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>بل</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr"/>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I739" t="n">
+        <v>5</v>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -42883,14 +42931,15 @@
         <v>96.66666666666667</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46148</v>
-      </c>
-      <c r="F70" s="1" t="n">
-        <v>46244.66666666666</v>
+        <v>46248</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>46344</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-05-06 | تم بواسطة: محمود ايهاب</t>
+          <t>2026-05-06 | تم بواسطة: محمود ايهاب
+2026-08-14 | تم بواسطة: بل</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -7715,7 +7715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K739"/>
+  <dimension ref="A1:K740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34920,6 +34920,51 @@
         </is>
       </c>
       <c r="K739" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>0</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>كرد1</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية ' فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن' بواسطة ي</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr"/>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I740" t="n">
+        <v>5</v>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -42933,7 +42978,7 @@
       <c r="E70" s="1" t="n">
         <v>46248</v>
       </c>
-      <c r="F70" s="2" t="n">
+      <c r="F70" s="1" t="n">
         <v>46344</v>
       </c>
       <c r="G70" t="inlineStr">
@@ -45647,16 +45692,17 @@
         <v>30</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46202</v>
-      </c>
-      <c r="F161" s="1" t="n">
-        <v>46232</v>
+        <v>46248</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>46278</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
           <t>2026-06-08 | تم بواسطة: تيم الكرد
 2026-06-08 | تم بواسطة: تيم الكرد
-2026-06-29 | تم بواسطة: تيم الكرد</t>
+2026-06-29 | تم بواسطة: تيم الكرد
+2026-08-14 | تم بواسطة: ي</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -29,11 +29,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,10 +62,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2894,6 +2891,48 @@
           <t>https://raw.githubusercontent.com/mahmedabdallh123/stations/main/event_images/event/event_e3e4a293_20260708_105207.jpg</t>
         </is>
       </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>7.5موتورkw</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ش</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>3</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -45694,7 +45733,7 @@
       <c r="E161" s="1" t="n">
         <v>46248</v>
       </c>
-      <c r="F161" s="2" t="n">
+      <c r="F161" s="1" t="n">
         <v>46278</v>
       </c>
       <c r="G161" t="inlineStr">

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2933,6 +2933,48 @@
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>7.5موتورkw</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ش</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>3</v>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -29,9 +29,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -62,9 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7796,7 +7799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K740"/>
+  <dimension ref="A1:K741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35046,6 +35049,51 @@
         </is>
       </c>
       <c r="K740" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>0</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>كرد10</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>صيانة وقائية: تغير اول جريده 240</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>تم تنفيذ الصيانة الدورية 'تغير اول جريده 240' بواسطة س</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr"/>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>صيانة وقائية</t>
+        </is>
+      </c>
+      <c r="I741" t="n">
+        <v>5</v>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>ملتزم بالكامل</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -43438,14 +43486,15 @@
         <v>96.66666666666667</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46123</v>
-      </c>
-      <c r="F81" s="1" t="n">
-        <v>46219</v>
+        <v>46248</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>46344</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-04-11 | تم بواسطة: ايهاب</t>
+          <t>2026-04-11 | تم بواسطة: ايهاب
+2026-08-14 | تم بواسطة: س</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -29,11 +29,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,10 +62,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -26918,12 +26915,12 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>صيانة وقائية: فحص عيارات رولين الكويلر ومنطقه الديلفري الخاصين بسير700,1270</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>تم تنفيذ الصيانة الدورية 'فحص عيارات رولين الكويلر ومنطقه الديلفري الخاصين بسير700,1270' بواسطة حسام ،محمود ايهاب</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
@@ -26967,12 +26964,12 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>صيانة وقائية: فحص عيارات رولين الكويلر ومنطقه الديلفري الخاصين بسير700,1270</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>تم تنفيذ الصيانة الدورية 'فحص عيارات رولين الكويلر ومنطقه الديلفري الخاصين بسير700,1270' بواسطة محمود ايهاب ،حسام</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
@@ -27421,12 +27418,12 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>صيانة وقائية: فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270' بواسطة مصطفى </t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
@@ -27703,12 +27700,12 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>صيانة وقائية: فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>تم تنفيذ الصيانة الدورية 'فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270' بواسطة محمود ايهاب</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
@@ -27752,12 +27749,12 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>صيانة وقائية: فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>تم تنفيذ الصيانة الدورية 'فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270' بواسطة محمود ايهاب</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
@@ -27850,12 +27847,12 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>صيانة وقائية: فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>تم تنفيذ الصيانة الدورية 'فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270' بواسطة محمود ايهاب</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
@@ -28112,12 +28109,12 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>صيانة وقائية: فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270' بواسطة محمود إيهاب </t>
+          <t>رصيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
@@ -28161,12 +28158,12 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>صيانة وقائية: فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270' بواسطة محمود إيهاب </t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
@@ -28210,12 +28207,12 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>صيانة وقائية: فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270' بواسطة محمود إيهاب </t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
@@ -28259,12 +28256,12 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>صيانة وقائية: فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270' بواسطة محمود إيهاب </t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
@@ -28493,12 +28490,12 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>صيانة وقائية: فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270</t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t xml:space="preserve">تم تنفيذ الصيانة الدورية 'فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير700وسير1270' بواسطة محمود ايهاب </t>
+          <t>صيانة وقائية:  فحص عيارات ومسافات رولين الكويلر والديليفري الخاصين بسير المسنن</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
@@ -34247,8 +34244,10 @@
       <c r="K720" t="inlineStr"/>
     </row>
     <row r="721">
-      <c r="A721" t="n">
-        <v>0</v>
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
@@ -34281,8 +34280,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="I721" t="n">
-        <v>5</v>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
@@ -34372,8 +34373,10 @@
       <c r="K723" t="inlineStr"/>
     </row>
     <row r="724">
-      <c r="A724" t="n">
-        <v>0</v>
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
@@ -34406,8 +34409,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="I724" t="n">
-        <v>5</v>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
@@ -34507,8 +34512,10 @@
       <c r="K726" t="inlineStr"/>
     </row>
     <row r="727">
-      <c r="A727" t="n">
-        <v>0</v>
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
@@ -34541,8 +34548,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="I727" t="n">
-        <v>5</v>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
@@ -34552,8 +34561,10 @@
       <c r="K727" t="inlineStr"/>
     </row>
     <row r="728">
-      <c r="A728" t="n">
-        <v>0</v>
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
@@ -34586,8 +34597,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="I728" t="n">
-        <v>5</v>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J728" t="inlineStr">
         <is>
@@ -35006,8 +35019,10 @@
       <c r="K739" t="inlineStr"/>
     </row>
     <row r="740">
-      <c r="A740" t="n">
-        <v>0</v>
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
@@ -35040,8 +35055,10 @@
           <t>صيانة وقائية</t>
         </is>
       </c>
-      <c r="I740" t="n">
-        <v>5</v>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J740" t="inlineStr">
         <is>
@@ -43488,7 +43505,7 @@
       <c r="E81" s="1" t="n">
         <v>46248</v>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="F81" s="1" t="n">
         <v>46344</v>
       </c>
       <c r="G81" t="inlineStr">

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3143,6 +3143,48 @@
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>مكبس التمشيط</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>قطع حصيره مكبس علويه</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>تم تركيب حصيره جديده</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>تبم</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>3</v>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3185,6 +3185,48 @@
       </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>7.5موتورkw</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>3</v>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -29,9 +29,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -62,9 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -49266,14 +49269,15 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46261</v>
-      </c>
-      <c r="F261" s="1" t="n">
-        <v>46261</v>
+        <v>46263</v>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>46263</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-08-27 | تم بواسطة: ل</t>
+          <t>2026-08-27 | تم بواسطة: ل
+2026-08-29 | تم بواسطة: ش</t>
         </is>
       </c>
       <c r="H261" t="inlineStr"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -29,11 +29,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,10 +62,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3230,6 +3227,48 @@
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>7.5موتورkw</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ن</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>3</v>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -49271,7 +49310,7 @@
       <c r="E261" s="1" t="n">
         <v>46263</v>
       </c>
-      <c r="F261" s="2" t="n">
+      <c r="F261" s="1" t="n">
         <v>46263</v>
       </c>
       <c r="G261" t="inlineStr">

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -29,9 +29,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -62,9 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -49214,11 +49217,17 @@
       <c r="D258" t="n">
         <v>180</v>
       </c>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="G258" t="inlineStr"/>
+      <c r="E258" s="1" t="n">
+        <v>46263</v>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>46443</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>2026-08-29 | تم بواسطة: ا</t>
+        </is>
+      </c>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
     </row>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -49190,11 +49190,17 @@
       <c r="D257" t="n">
         <v>180</v>
       </c>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="G257" t="inlineStr"/>
+      <c r="E257" s="1" t="n">
+        <v>46263</v>
+      </c>
+      <c r="F257" s="2" t="n">
+        <v>46443</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>2026-08-29 | تم بواسطة: ا</t>
+        </is>
+      </c>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
     </row>
@@ -49220,7 +49226,7 @@
       <c r="E258" s="1" t="n">
         <v>46263</v>
       </c>
-      <c r="F258" s="2" t="n">
+      <c r="F258" s="1" t="n">
         <v>46443</v>
       </c>
       <c r="G258" t="inlineStr">

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -41074,7 +41074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I261"/>
+  <dimension ref="A1:I262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49193,7 +49193,7 @@
       <c r="E257" s="1" t="n">
         <v>46263</v>
       </c>
-      <c r="F257" s="2" t="n">
+      <c r="F257" s="1" t="n">
         <v>46443</v>
       </c>
       <c r="G257" t="inlineStr">
@@ -49336,6 +49336,33 @@
       </c>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>كرد10</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>24 ساعة</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>صيانه شهرين</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" s="2" t="n">
+        <v>46264</v>
+      </c>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -41074,7 +41074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I262"/>
+  <dimension ref="A1:I263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49357,12 +49357,39 @@
         <v>1</v>
       </c>
       <c r="E262" t="inlineStr"/>
-      <c r="F262" s="2" t="n">
+      <c r="F262" s="1" t="n">
         <v>46264</v>
       </c>
       <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>كرد10</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>24 ساعة</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>صيانه شهرين</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" s="2" t="n">
+        <v>46264</v>
+      </c>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -29,11 +29,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,10 +62,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3272,6 +3269,48 @@
       </c>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>7.5موتورkw</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>نا</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>ميكانيكي</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>3</v>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -49384,7 +49423,7 @@
         <v>1</v>
       </c>
       <c r="E263" t="inlineStr"/>
-      <c r="F263" s="2" t="n">
+      <c r="F263" s="1" t="n">
         <v>46264</v>
       </c>
       <c r="G263" t="inlineStr"/>

--- a/l9.xlsx
+++ b/l9.xlsx
@@ -29,9 +29,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -62,9 +64,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -42940,16 +42943,17 @@
         <v>30</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46203</v>
-      </c>
-      <c r="F53" s="1" t="n">
-        <v>46233</v>
+        <v>46263</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>46293</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>2026-04-29 | تم بواسطة: تيم الكرد
 2026-05-26 | تم بواسطة: تيم الكرد
-2026-06-30 | تم بواسطة: تيم الكرد</t>
+2026-06-30 | تم بواسطة: تيم الكرد
+2026-08-29 | تم بواسطة: ل</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
